--- a/eval/Query.xlsx
+++ b/eval/Query.xlsx
@@ -777,6 +777,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>近</t>
     </r>
     <r>
@@ -1146,7 +1152,7 @@
 咨询类        8        0.1905</t>
   </si>
   <si>
-    <t>WITH cte AS (SELECT *  FROM shanghai_ad_time WHERE `内容描述` LIKE '%加装电梯%' AND MONTH(`工单生成时间`) BETWEEN 1 AND 6 AND YEAR(`工单生成时间`) = YEAR(CURDATE()))) SELECT `工单类型`, COUNT(*), COUNT(*) / (SELECT COUNT(*) FROM cte) FROM cte GROUP BY `工单类型` ORDER BY COUNT(*) DESC</t>
+    <t>WITH cte AS (SELECT *  FROM shanghai_ad_time WHERE `内容描述` LIKE '%加装电梯%' AND MONTH(`工单生成时间`) BETWEEN 1 AND 6 AND YEAR(`工单生成时间`) = YEAR(CURDATE())) SELECT `工单类型`, COUNT(*), COUNT(*) / (SELECT COUNT(*) FROM cte) FROM cte GROUP BY `工单类型` ORDER BY COUNT(*) DESC</t>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%积水%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `工单类型`='求助类'</t>
@@ -1188,10 +1194,10 @@
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%业委会管理不善%' AND YEAR(`工单生成时间`) = YEAR(CURDATE())</t>
   </si>
   <si>
-    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='审验登记' AND MONTH(`工单生成时间`) BETWEEN 1 AND 6 AND YEAR(`工单生成时间`) = YEAR(CURDATE())) AND `工单类型`='咨询类'</t>
-  </si>
-  <si>
-    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='入学政策' AND MONTH(`工单生成时间`) BETWEEN 1 AND 6 AND YEAR(`工单生成时间`) = YEAR(CURDATE())) AND `工单类型`='咨询类'</t>
+    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='审验登记' AND MONTH(`工单生成时间`) BETWEEN 1 AND 6 AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `工单类型`='咨询类'</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='入学政策' AND MONTH(`工单生成时间`) BETWEEN 1 AND 6 AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `工单类型`='咨询类'</t>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%市民举报某些商家雇佣存在无职业资质人员%'</t>
@@ -1901,6 +1907,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.75"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9.75"/>
+      <color rgb="FF1F2329"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1910,18 +1928,6 @@
       <sz val="10"/>
       <color rgb="FF1F2329"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color rgb="FF1F2329"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>

--- a/eval/Query.xlsx
+++ b/eval/Query.xlsx
@@ -1441,7 +1441,7 @@
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%京东金融%' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
-    <t>2024年医保政策咨询事件中哪种工单类型处理的最多</t>
+    <t>2025年医保政策咨询事件中哪种工单类型处理的最多</t>
   </si>
   <si>
     <t>咨询类        2311
@@ -1465,7 +1465,7 @@
     <t>SELECT `工单类型`, COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `工单类别`='次紧急' GROUP BY `工单类型` ORDER BY 总数 DESC LIMIT 1</t>
   </si>
   <si>
-    <t>2024年4月网上购物的投诉数量随天数的变化趋势</t>
+    <t>2025年4月网上购物的投诉数量随天数的变化趋势</t>
   </si>
   <si>
     <t>1        131
@@ -1503,7 +1503,7 @@
     <t>SELECT DAY(`工单生成时间`) AS 日, COUNT(*) AS 投诉数量 FROM shanghai_ad_time WHERE YEAR(`工单生成时间`)='2024' AND MONTH(`工单生成时间`)='4' AND `工单类型`='投诉举报类' GROUP BY 日 ORDER BY 日</t>
   </si>
   <si>
-    <t>2024年离婚办理事件随月份的变化趋势</t>
+    <t>2025年离婚办理事件随月份的变化趋势</t>
   </si>
   <si>
     <t>1        5
@@ -1523,7 +1523,7 @@
     <t>SELECT MONTH(`工单生成时间`) AS 月, COUNT(*) AS 数量 FROM shanghai_ad_time WHERE YEAR(`工单生成时间`)='2024' AND `四级分类`='离婚办理' GROUP BY 月 ORDER BY 月</t>
   </si>
   <si>
-    <t>2024年5月份浦东新区的交通违章事件的每周发生数量变化趋势</t>
+    <t>2025年5月份浦东新区的交通违章事件的每周发生数量变化趋势</t>
   </si>
   <si>
     <t>1        1
@@ -1536,19 +1536,19 @@
     <t>SELECT WEEK(`工单生成时间`) - WEEK(DATE_SUB('2024-05-01', INTERVAL 1 DAY)) + 1 AS 周数, COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='交通违章' AND `诉求区域`='浦东新区' AND YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=5 GROUP BY 周数 ORDER BY 周数</t>
   </si>
   <si>
-    <t>2024年6月份咨询工单比5月份的多多少</t>
+    <t>2025年6月份咨询工单比5月份的多多少</t>
   </si>
   <si>
     <t>WITH 六月 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=6 AND `工单类型`='咨询类'), 五月 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=5 AND `工单类型`='咨询类') SELECT 六月.总数 - 五月.总数 AS 差值 FROM 六月,五月</t>
   </si>
   <si>
-    <t>2024年6月份浦东的投诉工单量比虹口的多多少</t>
+    <t>2025年6月份浦东的投诉工单量比虹口的多多少</t>
   </si>
   <si>
     <t>WITH 浦东 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `诉求区域`='浦东新区' AND YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=6 AND `工单类型`='投诉举报类'), 虹口 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `诉求区域`='虹口区' AND YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=5 AND `工单类型`='投诉举报类') SELECT 浦东.总数 - 虹口.总数 AS 差值 FROM 浦东,虹口</t>
   </si>
   <si>
-    <t>2024年1月份社会管理类工单比公安政法类的多多少</t>
+    <t>2025年1月份社会管理类工单比公安政法类的多多少</t>
   </si>
   <si>
     <t>WITH 社会管理 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `一级分类`='社会管理类' AND YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=1), 公安政法 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `一级分类`='公安政法类' AND YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=1) SELECT 社会管理.总数 - 公安政法.总数 AS 差值 FROM 社会管理,公安政法</t>
@@ -1907,9 +1907,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9.75"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2329"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1919,15 +1925,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="9.75"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F2329"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>

--- a/eval/Query.xlsx
+++ b/eval/Query.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" activeTab="3"/>
+    <workbookView windowHeight="17775" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="全部Query" sheetId="2" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="418">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="604">
   <si>
     <t>近1个月虹口区发生了多少起城市管理类的投诉事件</t>
   </si>
@@ -774,6 +774,15 @@
   </si>
   <si>
     <t>SQL</t>
+  </si>
+  <si>
+    <t>MaskedQ</t>
+  </si>
+  <si>
+    <t>Mask</t>
+  </si>
+  <si>
+    <t>Masked</t>
   </si>
   <si>
     <r>
@@ -826,7 +835,69 @@
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `诉求区域`='虹口区' AND `三级分类`='城市管理' AND `工单生成时间` &gt; DATE_SUB(CURDATE(), INTERVAL 1 MONTH) AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
-    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `诉求区域`='浦东新区' AND `二级分类`='金融' AND `三级分类`='金融' AND `工单类型`='咨询类' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH)</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个月[诉求区域]发生了多少起[四级分类]类的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2329"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>[工单类型]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事件</t>
+    </r>
+  </si>
+  <si>
+    <t>诉求区域,四级分类,工单类型</t>
+  </si>
+  <si>
+    <t>虹口区,城市管理,投诉</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `诉求区域`='浦东新区' AND `二级分类`='金融' AND `工单类型`='咨询类' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH)</t>
+  </si>
+  <si>
+    <t>近3个月[诉求区域]发生了多少起[二级分类]类的[工单类型]事件</t>
+  </si>
+  <si>
+    <t>诉求区域,二级分类,工单类型</t>
+  </si>
+  <si>
+    <t>浦东,金融,咨询</t>
   </si>
   <si>
     <t>本市        1240
@@ -850,7 +921,16 @@
 崇明区        1</t>
   </si>
   <si>
-    <t>SELECT `诉求区域`, COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `工单类型`='投诉举报类' AND `四级分类`='网上购物' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) GROUP BY `诉求区域` ORDER BY 总数 DESC</t>
+    <t>SELECT `诉求区域`, COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `工单类型`='投诉举报类' AND `四级分类`='网上购物' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) GROUP BY `诉求区域` ORDER BY 总数 DESC LIMIT 10</t>
+  </si>
+  <si>
+    <t>近半年[四级分类]的[工单类型]事件主要分布在哪些区域</t>
+  </si>
+  <si>
+    <t>四级分类,工单类型</t>
+  </si>
+  <si>
+    <t>网上购物,投诉</t>
   </si>
   <si>
     <t>群众经常上报排堵保畅的路段有哪些?</t>
@@ -871,39 +951,31 @@
     <t>SELECT `诉求地址`, COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `四级分类` = '排堵保畅' GROUP BY `诉求地址` ORDER BY 总数 DESC LIMIT 10</t>
   </si>
   <si>
+    <t>群众经常上报[四级分类]的路段有哪些?</t>
+  </si>
+  <si>
+    <t>四级分类</t>
+  </si>
+  <si>
+    <t>排堵保畅</t>
+  </si>
+  <si>
     <t>万达广场发生了哪些投诉事件</t>
   </si>
   <si>
     <t>20240606035082        4500        2024-06-06 20:06:41        浦东新区张江晨晖路825弄        浦东新区        重复来电：市民反映相同问题。【最近办结的工单编号:20240507010443，工单内容:市民来电反映：上述地址是汤臣豪园二期，市民2023年5-6月的时候向物业交1800元的停车费，当时说可以停放半年（有微信转账记录），2023年9月由于物业换人，导致市民无法正常停车，联系对方物业，对方表示当时负责收取停车费的人不在职了，该问题会解决，但是一直没有下文。诉求：请管理部门协调退费或者可以正常停车。】        一般        已告知市民对于委办局明确且清晰的答复不予派单。市民不认可，申请主动挂机。        个人        建设交通类        住房保障        物业服务管理        物业安保                        综合服务        1717673799-671354        投诉举报类        住房和城乡建设类        住房保障        物业服务管理        停车管理        停车费</t>
   </si>
   <si>
-    <t>SELECT * FROM shanghai_ad_time WHERE `诉求地址` LIKE '%万达广场' AND `工单类型`='投诉举报类'</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF1F2329"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>今年涉及到</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9.75"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>私拆承重墙相关的事件有多少起?分别涉及到哪些地方?</t>
-    </r>
-  </si>
-  <si>
-    <t>NULL</t>
-  </si>
-  <si>
-    <t>SELECT * FROM shanghai_ad_time WHERE `内容描述` LIKE '%私拆承重墙%' AND YEAR(`工单生成时间`) = YEAR(CURDATE())</t>
+    <t>SELECT * FROM shanghai_ad_time WHERE `内容描述` LIKE '%万达广场%' AND `工单类型`='投诉举报类'</t>
+  </si>
+  <si>
+    <t>[诉求地址]发生了哪些[工单类型]事件</t>
+  </si>
+  <si>
+    <t>诉求地址,工单类型</t>
+  </si>
+  <si>
+    <t>万达广场,投诉</t>
   </si>
   <si>
     <t>宝山区        17
@@ -925,7 +997,16 @@
 青浦区        3</t>
   </si>
   <si>
-    <t>SELECT `诉求区域`, COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `内容描述` LIKE '%飞线充电%' OR `内容描述` LIKE '%电动车上楼%' GROUP BY `诉求区域`</t>
+    <t>SELECT `诉求区域`, COUNT(*) AS 总数 FROM shanghai_ad_time WHERE (`内容描述` LIKE '%飞线充电%' OR `内容描述` LIKE '%电动车上楼%') AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) GROUP BY `诉求区域`</t>
+  </si>
+  <si>
+    <t>三个月内涉及到[内容描述]和[内容描述]的事件有多少起?分别涉及到哪些地方?</t>
+  </si>
+  <si>
+    <t>内容描述,内容描述</t>
+  </si>
+  <si>
+    <t>飞线充电,电动车上楼</t>
   </si>
   <si>
     <t>本市        26
@@ -999,7 +1080,16 @@
 崇明区江南大道，潘圆公路        1</t>
   </si>
   <si>
-    <t>SELECT `诉求地址`, COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 10 DAY) AND `诉求区域`='浦东新区' AND `内容描述` LIKE '%违章停车%' OR `内容描述` LIKE '%闯红灯%' GROUP BY `诉求地址` ORDER BY 总数 DESC</t>
+    <t>SELECT `诉求地址`, COUNT(*) AS 总数 FROM shanghai_ad_time WHERE (`内容描述` LIKE '%违章停车%' OR `内容描述` LIKE '%闯红灯%')  AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 10 DAY) AND `诉求区域`='浦东新区' GROUP BY `诉求地址` ORDER BY 总数 DESC LIMIT 10</t>
+  </si>
+  <si>
+    <t>近10天内[诉求区域]哪些路段[内容描述]、[内容描述]的问题较多?</t>
+  </si>
+  <si>
+    <t>诉求区域,内容描述,内容描述</t>
+  </si>
+  <si>
+    <t>浦东,违章停车,闯红灯</t>
   </si>
   <si>
     <r>
@@ -1022,7 +1112,51 @@
     </r>
   </si>
   <si>
-    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `工单类型`='投诉举报类' AND `四级分类` LIKE '%物业%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 1 MONTH)</t>
+    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%物业举报%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 1 MONTH)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2329"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>近期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2329"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2329"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个月内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收到的[内容描述]的事件有多少起</t>
+    </r>
+  </si>
+  <si>
+    <t>内容描述</t>
+  </si>
+  <si>
+    <t>物业举报</t>
   </si>
   <si>
     <r>
@@ -1048,16 +1182,82 @@
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='物业安保' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH)</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF1F2329"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三个月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[四级分类]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事件有多少起</t>
+    </r>
+  </si>
+  <si>
+    <t>物业安保</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='物业管理不善' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
+    <t>最近半年[四级分类]的[工单类型]发生了多少起</t>
+  </si>
+  <si>
+    <t>物业管理不善,工单类型</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类` = '群租现象' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
+    <t>最近3个月的[四级分类]的[工单类型]有多少起</t>
+  </si>
+  <si>
+    <t>群租现象,投诉</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='物业维修添置' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH)</t>
   </si>
   <si>
+    <t>最近3个月[四级分类]事件发生了多少起</t>
+  </si>
+  <si>
+    <t>物业维修添置</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='垃圾清理' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `工单类型`='投诉举报类'</t>
+  </si>
+  <si>
+    <t>最近3个月[四级分类]相关[工单类型]有多少件</t>
+  </si>
+  <si>
+    <t>垃圾清理,投诉</t>
   </si>
   <si>
     <r>
@@ -1092,13 +1292,88 @@
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='物业管理收费' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH)</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最近</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>个月</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[四级分类]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事件发生了多少起</t>
+    </r>
+  </si>
+  <si>
+    <t>物业管理收费</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='绿化维护' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH)</t>
   </si>
   <si>
+    <t>最近半年[四级分类]事件反映了多少起</t>
+  </si>
+  <si>
+    <t>绿化维护</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%儿童游乐场所%' AND YEAR(`工单生成时间`) = YEAR(CURDATE())</t>
   </si>
   <si>
+    <t>今年[内容描述]相关[工单类型]有多少件</t>
+  </si>
+  <si>
+    <t>内容描述,工单类型</t>
+  </si>
+  <si>
+    <t>儿童游乐场所,投诉</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `客户类型`='企业' AND YEAR(`工单生成时间`) = YEAR(CURDATE())</t>
+  </si>
+  <si>
+    <t>今年上半年收到了多少[客户类型]服务类型的工单</t>
+  </si>
+  <si>
+    <t>客户类型</t>
+  </si>
+  <si>
+    <t>企业</t>
   </si>
   <si>
     <t>咨询类        2547        0.6256
@@ -1111,40 +1386,112 @@
     <t>WITH cte AS (SELECT *  FROM shanghai_ad_time WHERE `客户类型`='企业' AND YEAR(`工单生成时间`) = YEAR(CURDATE())) SELECT `工单类型`, COUNT(*), COUNT(*) / (SELECT COUNT(*) FROM cte) FROM cte GROUP BY `工单类型` ORDER BY COUNT(*) DESC</t>
   </si>
   <si>
+    <t>今年上半年[客户类型]服务工单里工单类型分别有那些，占比如何</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `客户类型`='企业' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `内容描述` LIKE '%网上办理%'</t>
   </si>
   <si>
+    <t>今年上半年[客户类型]服务中[内容描述]相关事件有多少件</t>
+  </si>
+  <si>
+    <t>客户类型,内容描述</t>
+  </si>
+  <si>
+    <t>企业,网上办理流程</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `客户类型`='企业' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新五级分类` = '注销登记'</t>
   </si>
   <si>
+    <t>企业,注销登记办理流程</t>
+  </si>
+  <si>
     <t>今年上半年企业服务中电子营业执照相关事件有多少件</t>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `客户类型`='企业' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `新五级分类` = '电子营业执照'</t>
   </si>
   <si>
+    <t>企业,电子营业执照</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `客户类型`='企业' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `四级分类` = '审验登记'</t>
   </si>
   <si>
-    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `工单类型`='咨询类' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `内容描述` LIKE '%社保办理%'</t>
-  </si>
-  <si>
-    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `内容描述` LIKE '%税务%'</t>
+    <t>今年上半年[客户类型]服务中[四级分类]相关事件有多少件</t>
+  </si>
+  <si>
+    <t>客户类型,四级分类</t>
+  </si>
+  <si>
+    <t>企业,审验登记</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `工单类型`='咨询类' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `内容描述` LIKE '%社保业务办理%'</t>
+  </si>
+  <si>
+    <t>今年有多少起[内容描述]的[工单类型]事件</t>
+  </si>
+  <si>
+    <t>社保业务办理,咨询</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `二级分类`='税务'</t>
+  </si>
+  <si>
+    <t>今年涉及[二级分类]相关事件有多少工单</t>
+  </si>
+  <si>
+    <t>二级分类</t>
+  </si>
+  <si>
+    <t>税务</t>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='违法建筑' AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
+    <t>涉及[四级分类]的[工单类型]有多少起</t>
+  </si>
+  <si>
+    <t>违法建筑,投诉</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%消费券%' AND `工单类型`='咨询类' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH)</t>
   </si>
   <si>
+    <t>近半年[内容描述]相关的[工单类型]事件有多少起</t>
+  </si>
+  <si>
+    <t>消费券,咨询</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%台风%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH)</t>
   </si>
   <si>
+    <t>近半年[四级分类]造成的事件有多少起</t>
+  </si>
+  <si>
+    <t>台风</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%加装电梯%' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
+    <t>今年内[内容描述]的[工单类型]有多少起</t>
+  </si>
+  <si>
+    <t>加装电梯,投诉</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%加装电梯%' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `工单类型`='咨询类'</t>
+  </si>
+  <si>
+    <t>今年内[内容描述]的[工单类型]工单有多少起</t>
+  </si>
+  <si>
+    <t>加装电梯,咨询</t>
   </si>
   <si>
     <t>求助类        25        0.5952
@@ -1155,16 +1502,49 @@
     <t>WITH cte AS (SELECT *  FROM shanghai_ad_time WHERE `内容描述` LIKE '%加装电梯%' AND MONTH(`工单生成时间`) BETWEEN 1 AND 6 AND YEAR(`工单生成时间`) = YEAR(CURDATE())) SELECT `工单类型`, COUNT(*), COUNT(*) / (SELECT COUNT(*) FROM cte) FROM cte GROUP BY `工单类型` ORDER BY COUNT(*) DESC</t>
   </si>
   <si>
-    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%积水%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `工单类型`='求助类'</t>
+    <t>这个月[内容描述]的工单类型有哪些，占比有多少</t>
+  </si>
+  <si>
+    <t>加装电梯</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%小区积水%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `工单类型`='求助类'</t>
+  </si>
+  <si>
+    <t>近半年[内容描述]相关的[工单类型]工单有多少件</t>
+  </si>
+  <si>
+    <t>小区积水,求助</t>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%房屋漏水%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH)</t>
   </si>
   <si>
+    <t>近半年[内容描述]事件发生了多少起</t>
+  </si>
+  <si>
+    <t>房屋漏水</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%台风%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `工单类型`='咨询类'</t>
   </si>
   <si>
+    <t>与[四级分类]相关的[工单类型]工单有多少条</t>
+  </si>
+  <si>
+    <t>台风,诉求</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%台风%' AND `内容描述` LIKE '%树木倒伏%'</t>
+  </si>
+  <si>
+    <t>由[四级分类]造成的[内容描述]事件有多少起</t>
+  </si>
+  <si>
+    <t>四级分类,内容描述</t>
+  </si>
+  <si>
+    <t>台风,树木倒伏</t>
   </si>
   <si>
     <t>浦东新区        6
@@ -1185,28 +1565,94 @@
     <t>SELECT `诉求区域`, COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%台风%' AND `内容描述` LIKE '%倒伏%' GROUP BY `诉求区域` ORDER BY COUNT(*) DESC</t>
   </si>
   <si>
-    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%台风%' AND `内容描述` LIKE '%停课%' AND `工单类型`='投诉举报类'</t>
+    <t>跟[四级分类]造成的[内容描述]事件有关的[工单类型]所涉及的地方有那些</t>
+  </si>
+  <si>
+    <t>四级分类,内容描述,工单类型</t>
+  </si>
+  <si>
+    <t>台风,倒伏,投诉</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%台风%' AND `内容描述` LIKE '%学校该停课不停课%' AND `工单类型`='投诉举报类'</t>
+  </si>
+  <si>
+    <t>[四级分类]造成的[内容描述]的[工单类型]有多少起</t>
+  </si>
+  <si>
+    <t>台风,学校该停课不停课,投诉</t>
+  </si>
+  <si>
+    <t>台风造成的道路积水影响市民出行的事件有多少起</t>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%台风%' AND `四级分类`='市政道路积水'</t>
   </si>
   <si>
+    <t>[四级分类]造成的[内容描述]的事件有多少起</t>
+  </si>
+  <si>
+    <t>台风,道路积水影响市民出行</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%业委会管理不善%' AND YEAR(`工单生成时间`) = YEAR(CURDATE())</t>
   </si>
   <si>
+    <t>今年[四级分类][内容描述]问题有多少起</t>
+  </si>
+  <si>
+    <t>业委会,管理不善</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='审验登记' AND MONTH(`工单生成时间`) BETWEEN 1 AND 6 AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `工单类型`='咨询类'</t>
   </si>
   <si>
+    <t>本月有多少起[四级分类]的[工单类型]业务</t>
+  </si>
+  <si>
+    <t>工商审验登记,咨询</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='入学政策' AND MONTH(`工单生成时间`) BETWEEN 1 AND 6 AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `工单类型`='咨询类'</t>
   </si>
   <si>
+    <t>本月[四级分类]相关[工单类型]工单有多少起</t>
+  </si>
+  <si>
+    <t>入学政策,咨询</t>
+  </si>
+  <si>
+    <t>NULL</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%市民举报某些商家雇佣存在无职业资质人员%'</t>
   </si>
   <si>
+    <t>市民举报某些[内容描述]的事件有多少起</t>
+  </si>
+  <si>
+    <t>商家雇佣存在无职业资质人员</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类` LIKE '%医保%' AND `工单类型`='咨询类' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH)</t>
   </si>
   <si>
+    <t>近半年[三级分类]相关的[工单类型]事件有多少起</t>
+  </si>
+  <si>
+    <t>三级分类,工单类型</t>
+  </si>
+  <si>
+    <t>医保,咨询</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='医保报销' AND `工单类型`='投诉举报类'</t>
+  </si>
+  <si>
+    <t>[四级分类]的[工单类型]事件有多少起</t>
+  </si>
+  <si>
+    <t>医保报销,投诉</t>
   </si>
   <si>
     <t xml:space="preserve">        615
@@ -1224,7 +1670,19 @@
     <t>SELECT `主办单位`, COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='拖欠工资' GROUP BY `主办单位` ORDER BY COUNT(*) DESC LIMIT 10</t>
   </si>
   <si>
+    <t>[四级分类]的主责部门是哪个</t>
+  </si>
+  <si>
+    <t>拖欠工资</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%表扬%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH)</t>
+  </si>
+  <si>
+    <t>半年内有多少[三级分类]相关的工单</t>
+  </si>
+  <si>
+    <t>表扬</t>
   </si>
   <si>
     <t xml:space="preserve">        50102
@@ -1242,6 +1700,12 @@
     <t>SELECT `主办单位`, COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='网上购物' GROUP BY `主办单位` ORDER BY COUNT(*) DESC LIMIT 10</t>
   </si>
   <si>
+    <t>[四级分类]的{主办单位]有哪些</t>
+  </si>
+  <si>
+    <t>网上购物</t>
+  </si>
+  <si>
     <t>道路积水问题通常由哪个部门负责处理</t>
   </si>
   <si>
@@ -1260,10 +1724,22 @@
     <t>SELECT `主办单位`, COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='市政道路积水' GROUP BY `主办单位` ORDER BY COUNT(*) DESC LIMIT 10</t>
   </si>
   <si>
+    <t>[四级分类]问题通常由哪个[主办单位]</t>
+  </si>
+  <si>
+    <t>道路积水</t>
+  </si>
+  <si>
     <t>最近一个月劳动争议的投诉数量是多少</t>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='劳动争议' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 1 MONTH)</t>
+  </si>
+  <si>
+    <t>最近一个月[四级分类]的[工单类型]数量是多少</t>
+  </si>
+  <si>
+    <t>劳动争议,投诉</t>
   </si>
   <si>
     <t>投诉举报类        1156        0.8588
@@ -1276,12 +1752,30 @@
     <t>WITH cte AS (SELECT *  FROM shanghai_ad_time WHERE `四级分类`='违法建筑' ) SELECT `工单类型`, COUNT(*), COUNT(*) / (SELECT COUNT(*) FROM cte) FROM cte GROUP BY `工单类型` ORDER BY COUNT(*) DESC</t>
   </si>
   <si>
+    <t>[内容描述]相关的工单中，各类工单（[工单类型]、[工单类型]、[工单类型]、[工单类型]、[工单类型]）的比例是多少</t>
+  </si>
+  <si>
+    <t>内容描述,工单类型,工单类型,工单类型,工单类型,工单类型</t>
+  </si>
+  <si>
+    <t>违章建筑,诉求类,投诉类,资讯类,建议类,其他类</t>
+  </si>
+  <si>
     <t>投诉举报类        121        0.8897
 咨询类        8        0.0588
 求助类        7        0.0515</t>
   </si>
   <si>
     <t>WITH cte AS (SELECT *  FROM shanghai_ad_time WHERE `四级分类`='居改非' ) SELECT `工单类型`, COUNT(*), COUNT(*) / (SELECT COUNT(*) FROM cte) FROM cte GROUP BY `工单类型` ORDER BY COUNT(*) DESC</t>
+  </si>
+  <si>
+    <t>[四级分类]的工单中，各类[工单类型]、[工单类型]、[工单类型]、[工单类型]的比例是多少</t>
+  </si>
+  <si>
+    <t>四级分类,工单类型,工单类型,工单类型,工单类型</t>
+  </si>
+  <si>
+    <t>小区居改非,诉求,投诉,咨询,建议</t>
   </si>
   <si>
     <t>浦东新区        8
@@ -1299,6 +1793,12 @@
     <t>SELECT `诉求区域`, COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%破坏承重墙%' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) GROUP BY `诉求区域` ORDER BY COUNT(*) DESC LIMIT 10</t>
   </si>
   <si>
+    <t>今年哪些区域有[内容描述]的情况发生</t>
+  </si>
+  <si>
+    <t>破坏承重墙</t>
+  </si>
+  <si>
     <t>浦东新区        130
 黄浦区        86
 本市        66
@@ -1314,10 +1814,22 @@
     <t>SELECT `诉求区域`, COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%动迁%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) GROUP BY `诉求区域` ORDER BY COUNT(*) DESC LIMIT 10</t>
   </si>
   <si>
+    <t>最近三个月哪些区域的居民有[内容描述]</t>
+  </si>
+  <si>
+    <t>动迁需求</t>
+  </si>
+  <si>
     <t>老旧小区改造的工单投诉量有多少</t>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%老旧小区改造%' AND `工单类型`='投诉举报类'</t>
+  </si>
+  <si>
+    <t>[内容描述]的工单[工单类型]量有多少</t>
+  </si>
+  <si>
+    <t>老旧小区改造,投诉</t>
   </si>
   <si>
     <t>处理服务态度问题最多的主办单位是哪个</t>
@@ -1338,13 +1850,31 @@
     <t>SELECT `主办单位`, COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='服务态度' GROUP BY `主办单位` ORDER BY COUNT(*) DESC LIMIT 10</t>
   </si>
   <si>
+    <t>处理[四级分类]问题最多的主办单位是哪个</t>
+  </si>
+  <si>
+    <t>服务态度</t>
+  </si>
+  <si>
     <t>近半年有多少起医疗纠纷的投诉事件</t>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类` = '医疗纠纷' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND  `工单类型`='投诉举报类'</t>
   </si>
   <si>
+    <t>近半年有多少起[四级分类]的[工单类型]事件</t>
+  </si>
+  <si>
+    <t>医疗纠纷,投诉</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%小区垃圾%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 1 MONTH) AND `工单类型`='投诉举报类'</t>
+  </si>
+  <si>
+    <t>最近一个月[内容描述][工单类型]的数量是多少</t>
+  </si>
+  <si>
+    <t>小区垃圾,投诉</t>
   </si>
   <si>
     <t>青浦区        8
@@ -1362,6 +1892,12 @@
     <t>SELECT `诉求区域`, COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%小区垃圾%' AND `工单类型`='投诉举报类' GROUP BY `诉求区域` ORDER BY COUNT(*) DESC LIMIT 10</t>
   </si>
   <si>
+    <t>[内容描述][工单类型]事件主要分布在哪些区</t>
+  </si>
+  <si>
+    <t>垃圾,投诉</t>
+  </si>
+  <si>
     <t>浦东新区        50
 闵行区        19
 普陀区        17
@@ -1377,7 +1913,16 @@
     <t>SELECT `诉求区域`, COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='油烟扰民' GROUP BY `诉求区域` ORDER BY COUNT(*) DESC LIMIT 10</t>
   </si>
   <si>
+    <t>哪些地方的[四级分类]事件比较多</t>
+  </si>
+  <si>
+    <t>油烟扰民</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='油烟扰民' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 1 MONTH) AND `工单类型`='投诉举报类'</t>
+  </si>
+  <si>
+    <t>油烟扰民,投诉</t>
   </si>
   <si>
     <t>投诉举报类        61        0.9104
@@ -1387,6 +1932,12 @@
   </si>
   <si>
     <t>WITH cte AS (SELECT *  FROM shanghai_ad_time WHERE `内容描述` LIKE '%居委会不作为%' ) SELECT `工单类型`, COUNT(*), COUNT(*) / (SELECT COUNT(*) FROM cte) FROM cte GROUP BY `工单类型` ORDER BY COUNT(*) DESC</t>
+  </si>
+  <si>
+    <t>[内容描述]的工单中，[工单类型]的比例是多少</t>
+  </si>
+  <si>
+    <t>居委会不作为,各类诉求</t>
   </si>
   <si>
     <t>求助类        99        0.4737
@@ -1399,46 +1950,130 @@
     <t>WITH cte AS (SELECT *  FROM shanghai_ad_time WHERE `内容描述` LIKE '%电瓶车充电%' ) SELECT `工单类型`, COUNT(*), COUNT(*) / (SELECT COUNT(*) FROM cte) FROM cte GROUP BY `工单类型` ORDER BY COUNT(*) DESC</t>
   </si>
   <si>
+    <t>相关的工单中，各类[工单类型]、[工单类型]、[工单类型]、[工单类型]的比例是多少</t>
+  </si>
+  <si>
+    <t>内容描述,工单类型,工单类型,工单类型,工单类型</t>
+  </si>
+  <si>
+    <t>电瓶车充电,诉求,投诉,咨询,建议</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%诈骗%' AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
+    <t>今年市民来[工单类型]被[内容描述]的工单有多少</t>
+  </si>
+  <si>
+    <t>工单类型,内容描述</t>
+  </si>
+  <si>
+    <t>投诉,被诈骗</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `新五级分类`='残疾证换证补证' AND YEAR(`工单生成时间`) = YEAR(CURDATE())</t>
   </si>
   <si>
+    <t>今年市民[工单类型][内容描述]的事件有多少起</t>
+  </si>
+  <si>
+    <t>咨询,办理残疾证到期换证</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%咸鱼平台%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
+    <t>3个月内有多少起[工单类型][内容描述]的事件</t>
+  </si>
+  <si>
+    <t>投诉,咸鱼平台</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%学校%' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
+    <t>今年[工单类型][内容描述]的事件有多少起</t>
+  </si>
+  <si>
+    <t>投诉,学校</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%医院%' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
+    <t>投诉,医院</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%医保断缴%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `工单类型`='咨询类'</t>
   </si>
   <si>
+    <t>近3个月[内容描述]的[工单类型]事件有多少起</t>
+  </si>
+  <si>
+    <t>医保断缴,咨询</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='人才引进' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 2 MONTH) AND `工单类型`='咨询类'</t>
   </si>
   <si>
+    <t>近2个月有多少[工单类型][四级分类]政策的工单</t>
+  </si>
+  <si>
+    <t>工单类型,四级分类</t>
+  </si>
+  <si>
+    <t>咨询,人才引进</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%支付宝%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH) AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
+    <t>近3个月[工单类型][内容描述]的工单有多少起</t>
+  </si>
+  <si>
+    <t>投诉,支付宝平台</t>
+  </si>
+  <si>
     <t>近3个月拖欠工资的事件有多少起</t>
   </si>
   <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%拖欠工资%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH)</t>
   </si>
   <si>
+    <t>近3个月[四级分类]的事件有多少起</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%上班猝死%' AND YEAR(`工单生成时间`) = YEAR(CURDATE())</t>
   </si>
   <si>
+    <t>今年反映[内容描述]的事件有多少起</t>
+  </si>
+  <si>
+    <t>上班猝死</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%无法挂号%' AND `四级分类` LIKE '%医保%' AND `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 3 MONTH)</t>
   </si>
   <si>
+    <t>近3个月因[三级分类]问题[内容描述]的事件有多少起</t>
+  </si>
+  <si>
+    <t>三级分类,内容描述</t>
+  </si>
+  <si>
+    <t>医保,无法挂号</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%平安金融%' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `工单类型`='投诉举报类'</t>
   </si>
   <si>
+    <t>平安金融,投诉</t>
+  </si>
+  <si>
     <t>SELECT COUNT(*) FROM shanghai_ad_time WHERE `内容描述` LIKE '%京东金融%' AND YEAR(`工单生成时间`) = YEAR(CURDATE()) AND `工单类型`='投诉举报类'</t>
+  </si>
+  <si>
+    <t>京东金融,投诉</t>
   </si>
   <si>
     <t>2025年医保政策咨询事件中哪种工单类型处理的最多</t>
@@ -1453,16 +2088,37 @@
     <t>SELECT `工单类型`, COUNT(*) AS 总数 FROM shanghai_ad_time WHERE YEAR(`工单生成时间`) = '2024' AND `四级分类`='医保政策咨询' GROUP BY `工单类型` ORDER BY 总数 DESC</t>
   </si>
   <si>
+    <t>2025年[四级分类]事件中哪种工单类型处理的最多</t>
+  </si>
+  <si>
+    <t>医保政策咨询</t>
+  </si>
+  <si>
     <t>近半年治安维护处理最多的主办单位是哪个</t>
   </si>
   <si>
     <t>SELECT `工单类型`, COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `工单生成时间`&gt; DATE_SUB(CURDATE(), INTERVAL 6 MONTH) AND `四级分类`='治安维护' GROUP BY `工单类型` ORDER BY 总数 DESC LIMIT 1</t>
   </si>
   <si>
+    <t>近半年[四级分类]处理最多的主办单位是哪个</t>
+  </si>
+  <si>
+    <t>治安维护</t>
+  </si>
+  <si>
     <t>次紧急工单的工单类型最多的是哪种</t>
   </si>
   <si>
     <t>SELECT `工单类型`, COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `工单类别`='次紧急' GROUP BY `工单类型` ORDER BY 总数 DESC LIMIT 1</t>
+  </si>
+  <si>
+    <t>[工单类别]工单的工单类型最多的是哪种</t>
+  </si>
+  <si>
+    <t>工单类别</t>
+  </si>
+  <si>
+    <t>次紧急</t>
   </si>
   <si>
     <t>2025年4月网上购物的投诉数量随天数的变化趋势</t>
@@ -1503,6 +2159,9 @@
     <t>SELECT DAY(`工单生成时间`) AS 日, COUNT(*) AS 投诉数量 FROM shanghai_ad_time WHERE YEAR(`工单生成时间`)='2024' AND MONTH(`工单生成时间`)='4' AND `工单类型`='投诉举报类' GROUP BY 日 ORDER BY 日</t>
   </si>
   <si>
+    <t>2025年4月[四级分类]的[工单类型]数量随天数的变化趋势</t>
+  </si>
+  <si>
     <t>2025年离婚办理事件随月份的变化趋势</t>
   </si>
   <si>
@@ -1523,6 +2182,12 @@
     <t>SELECT MONTH(`工单生成时间`) AS 月, COUNT(*) AS 数量 FROM shanghai_ad_time WHERE YEAR(`工单生成时间`)='2024' AND `四级分类`='离婚办理' GROUP BY 月 ORDER BY 月</t>
   </si>
   <si>
+    <t>2025年[四级分类]事件随月份的变化趋势</t>
+  </si>
+  <si>
+    <t>离婚办理</t>
+  </si>
+  <si>
     <t>2025年5月份浦东新区的交通违章事件的每周发生数量变化趋势</t>
   </si>
   <si>
@@ -1536,22 +2201,58 @@
     <t>SELECT WEEK(`工单生成时间`) - WEEK(DATE_SUB('2024-05-01', INTERVAL 1 DAY)) + 1 AS 周数, COUNT(*) FROM shanghai_ad_time WHERE `四级分类`='交通违章' AND `诉求区域`='浦东新区' AND YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=5 GROUP BY 周数 ORDER BY 周数</t>
   </si>
   <si>
+    <t>2025年5月份[诉求区域]的[四级分类]事件的每周发生数量变化趋势</t>
+  </si>
+  <si>
+    <t>诉求区域,四级分类</t>
+  </si>
+  <si>
+    <t>浦东新区,交通违章</t>
+  </si>
+  <si>
     <t>2025年6月份咨询工单比5月份的多多少</t>
   </si>
   <si>
     <t>WITH 六月 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=6 AND `工单类型`='咨询类'), 五月 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=5 AND `工单类型`='咨询类') SELECT 六月.总数 - 五月.总数 AS 差值 FROM 六月,五月</t>
   </si>
   <si>
+    <t>2025年6月份[工单类型]工单比5月份的多多少</t>
+  </si>
+  <si>
+    <t>工单类型</t>
+  </si>
+  <si>
+    <t>咨询</t>
+  </si>
+  <si>
     <t>2025年6月份浦东的投诉工单量比虹口的多多少</t>
   </si>
   <si>
     <t>WITH 浦东 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `诉求区域`='浦东新区' AND YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=6 AND `工单类型`='投诉举报类'), 虹口 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `诉求区域`='虹口区' AND YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=5 AND `工单类型`='投诉举报类') SELECT 浦东.总数 - 虹口.总数 AS 差值 FROM 浦东,虹口</t>
   </si>
   <si>
+    <t>2025年6月份[诉求区域]的[工单类型]工单量比[诉求区域]的多多少</t>
+  </si>
+  <si>
+    <t>诉求区域,工单类型,诉求区域</t>
+  </si>
+  <si>
+    <t>浦东,投诉,虹口</t>
+  </si>
+  <si>
     <t>2025年1月份社会管理类工单比公安政法类的多多少</t>
   </si>
   <si>
     <t>WITH 社会管理 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `一级分类`='社会管理类' AND YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=1), 公安政法 AS (SELECT COUNT(*) AS 总数 FROM shanghai_ad_time WHERE `一级分类`='公安政法类' AND YEAR(`工单生成时间`)=2024 AND MONTH(`工单生成时间`)=1) SELECT 社会管理.总数 - 公安政法.总数 AS 差值 FROM 社会管理,公安政法</t>
+  </si>
+  <si>
+    <t>2025年1月份[一级分类]工单比[一级分类]的多多少</t>
+  </si>
+  <si>
+    <t>一级分类,一级分类</t>
+  </si>
+  <si>
+    <t>社会管理类,公安政法类</t>
   </si>
   <si>
     <t>近10天合肥市蜀山区上报了多少起道路积水的问题？</t>
@@ -1699,7 +2400,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="35">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1740,6 +2441,12 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2329"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9.75"/>
@@ -1914,13 +2621,20 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF1F2329"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9.75"/>
-      <color rgb="FF1F2329"/>
+      <color rgb="FF14C0FF"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -1932,7 +2646,7 @@
     </font>
     <font>
       <sz val="9.75"/>
-      <color rgb="FF14C0FF"/>
+      <color rgb="FF1F2329"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -2284,31 +2998,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2317,119 +3028,122 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2473,6 +3187,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2534,13 +3251,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2816,7 +3526,7 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
@@ -2828,7 +3538,7 @@
       <c r="A2" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13"/>
+      <c r="B2" s="14"/>
       <c r="C2" s="9" t="s">
         <v>4</v>
       </c>
@@ -2837,7 +3547,7 @@
       <c r="A3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="13"/>
+      <c r="B3" s="14"/>
       <c r="C3" s="9" t="s">
         <v>6</v>
       </c>
@@ -2846,7 +3556,7 @@
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="13"/>
+      <c r="B4" s="14"/>
       <c r="C4" s="9" t="s">
         <v>8</v>
       </c>
@@ -2855,7 +3565,7 @@
       <c r="A5" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="13"/>
+      <c r="B5" s="14"/>
       <c r="C5" s="9" t="s">
         <v>10</v>
       </c>
@@ -2864,25 +3574,25 @@
       <c r="A6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="13"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="9" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" ht="19" customHeight="1" spans="1:4">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="13"/>
+      <c r="B7" s="14"/>
       <c r="D7" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:4">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="13"/>
+      <c r="B8" s="14"/>
       <c r="C8" s="9" t="s">
         <v>16</v>
       </c>
@@ -2894,7 +3604,7 @@
       <c r="A9" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="13"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="9" t="s">
         <v>19</v>
       </c>
@@ -2903,7 +3613,7 @@
       <c r="A10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="13"/>
+      <c r="B10" s="14"/>
       <c r="C10" s="9" t="s">
         <v>21</v>
       </c>
@@ -2913,7 +3623,7 @@
       <c r="A11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="13"/>
+      <c r="B11" s="14"/>
       <c r="C11" s="9" t="s">
         <v>23</v>
       </c>
@@ -3677,7 +4387,7 @@
       </c>
     </row>
     <row r="130" spans="1:1">
-      <c r="A130" s="14" t="s">
+      <c r="A130" s="15" t="s">
         <v>195</v>
       </c>
     </row>
@@ -3687,12 +4397,12 @@
       </c>
     </row>
     <row r="132" spans="1:1">
-      <c r="A132" s="14" t="s">
+      <c r="A132" s="15" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="133" spans="1:1">
-      <c r="A133" s="14" t="s">
+      <c r="A133" s="15" t="s">
         <v>198</v>
       </c>
     </row>
@@ -3732,7 +4442,7 @@
       </c>
     </row>
     <row r="141" spans="1:1">
-      <c r="A141" s="14" t="s">
+      <c r="A141" s="15" t="s">
         <v>206</v>
       </c>
     </row>
@@ -3837,7 +4547,7 @@
       </c>
     </row>
     <row r="162" spans="1:1">
-      <c r="A162" s="14" t="s">
+      <c r="A162" s="15" t="s">
         <v>227</v>
       </c>
     </row>
@@ -4188,12 +4898,12 @@
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="14" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1" spans="1:3">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="14" t="s">
         <v>230</v>
       </c>
       <c r="B28" s="9" t="s">
@@ -4204,12 +4914,12 @@
       </c>
     </row>
     <row r="29" ht="19" customHeight="1" spans="1:1">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="14" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="30" ht="19" customHeight="1" spans="1:2">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="14" t="s">
         <v>234</v>
       </c>
       <c r="B30" s="9" t="s">
@@ -4220,7 +4930,7 @@
       <c r="A31" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="15" t="s">
         <v>236</v>
       </c>
     </row>
@@ -4323,12 +5033,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R204"/>
+  <dimension ref="A1:R203"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="77" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="125" customWidth="1"/>
+    <col min="13" max="13" width="77" customWidth="1"/>
+    <col min="14" max="14" width="29.8571428571429" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="19" customHeight="1" spans="1:18">
@@ -4346,29 +5058,44 @@
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
+      <c r="I1" s="6" t="s">
+        <v>241</v>
+      </c>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
+      <c r="M1" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>243</v>
+      </c>
       <c r="O1" s="6"/>
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:14">
       <c r="A2" s="7" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B2" s="8">
         <v>14</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>245</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="N2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="9" t="s">
         <v>3</v>
       </c>
@@ -4376,928 +5103,1658 @@
         <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="4" ht="255" spans="1:3">
+        <v>249</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="N3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="4" ht="255" spans="1:14">
       <c r="A4" s="9" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>254</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="9" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>260</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="M5" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N5" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="11" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="9" t="s">
-        <v>252</v>
+        <v>266</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>270</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="I7" t="s">
+        <v>272</v>
+      </c>
+      <c r="M7" t="s">
+        <v>273</v>
+      </c>
+      <c r="N7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="I8" t="s">
+        <v>277</v>
+      </c>
+      <c r="M8" t="s">
+        <v>278</v>
+      </c>
+      <c r="N8" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B9" s="8">
+        <v>1658</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" s="8">
+        <v>2154</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="8">
+        <v>738</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="I11" t="s">
+        <v>290</v>
+      </c>
+      <c r="M11" t="s">
         <v>256</v>
       </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
+      <c r="N11" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="8">
+        <v>143</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="I12" t="s">
+        <v>293</v>
+      </c>
+      <c r="M12" t="s">
+        <v>256</v>
+      </c>
+      <c r="N12" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="8">
+        <v>1971</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="I13" t="s">
+        <v>296</v>
+      </c>
+      <c r="M13" t="s">
+        <v>262</v>
+      </c>
+      <c r="N13" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="8">
+        <v>208</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="I14" t="s">
+        <v>299</v>
+      </c>
+      <c r="M14" t="s">
+        <v>256</v>
+      </c>
+      <c r="N14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="B15" s="8">
+        <v>318</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="8">
+        <v>281</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="I16" t="s">
+        <v>306</v>
+      </c>
+      <c r="M16" t="s">
+        <v>262</v>
+      </c>
+      <c r="N16" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" s="8">
+        <v>5</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>308</v>
+      </c>
+      <c r="I17" t="s">
+        <v>309</v>
+      </c>
+      <c r="M17" t="s">
+        <v>310</v>
+      </c>
+      <c r="N17" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="8">
+        <v>4071</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>314</v>
+      </c>
+      <c r="N18" s="9" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="I19" t="s">
+        <v>318</v>
+      </c>
+      <c r="M19" t="s">
+        <v>314</v>
+      </c>
+      <c r="N19" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" s="8">
+        <v>39</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="I20" t="s">
+        <v>320</v>
+      </c>
+      <c r="M20" t="s">
+        <v>321</v>
+      </c>
+      <c r="N20" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="8">
+        <v>16</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="I21" t="s">
+        <v>320</v>
+      </c>
+      <c r="M21" t="s">
+        <v>321</v>
+      </c>
+      <c r="N21" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="B22" s="8">
+        <v>375</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="M22" t="s">
+        <v>321</v>
+      </c>
+      <c r="N22" s="9" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
+      <c r="A23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="8">
+        <v>1</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="I23" t="s">
+        <v>329</v>
+      </c>
+      <c r="M23" t="s">
+        <v>330</v>
+      </c>
+      <c r="N23" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="8">
+        <v>4</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="I24" t="s">
+        <v>333</v>
+      </c>
+      <c r="M24" t="s">
+        <v>310</v>
+      </c>
+      <c r="N24" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="8">
+        <v>872</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="I25" t="s">
+        <v>336</v>
+      </c>
+      <c r="M25" t="s">
+        <v>337</v>
+      </c>
+      <c r="N25" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B26" s="8">
+        <v>1156</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="I26" t="s">
+        <v>340</v>
+      </c>
+      <c r="M26" t="s">
+        <v>256</v>
+      </c>
+      <c r="N26" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
+      <c r="A27" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="8">
+        <v>16</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="I27" t="s">
+        <v>343</v>
+      </c>
+      <c r="M27" t="s">
+        <v>310</v>
+      </c>
+      <c r="N27" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="8">
+        <v>839</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="I28" t="s">
+        <v>346</v>
+      </c>
+      <c r="M28" t="s">
+        <v>262</v>
+      </c>
+      <c r="N28" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="8">
+        <v>130</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="I29" t="s">
+        <v>349</v>
+      </c>
+      <c r="M29" t="s">
+        <v>310</v>
+      </c>
+      <c r="N29" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="8">
+        <v>68</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="I30" t="s">
+        <v>352</v>
+      </c>
+      <c r="M30" t="s">
+        <v>310</v>
+      </c>
+      <c r="N30" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="I31" t="s">
+        <v>356</v>
+      </c>
+      <c r="M31" t="s">
+        <v>283</v>
+      </c>
+      <c r="N31" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B32" s="8">
+        <v>518</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="I32" t="s">
+        <v>359</v>
+      </c>
+      <c r="M32" t="s">
+        <v>310</v>
+      </c>
+      <c r="N32" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14">
+      <c r="A33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="8">
+        <v>96</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="I33" t="s">
+        <v>362</v>
+      </c>
+      <c r="M33" t="s">
+        <v>283</v>
+      </c>
+      <c r="N33" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="A34" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="8">
+        <v>68</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="I34" t="s">
+        <v>365</v>
+      </c>
+      <c r="M34" t="s">
+        <v>256</v>
+      </c>
+      <c r="N34" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="A35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="8">
+        <v>8</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="I35" t="s">
+        <v>368</v>
+      </c>
+      <c r="M35" t="s">
+        <v>369</v>
+      </c>
+      <c r="N35" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14">
+      <c r="A36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="I36" t="s">
+        <v>373</v>
+      </c>
+      <c r="M36" t="s">
+        <v>374</v>
+      </c>
+      <c r="N36" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="A37" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" s="8">
+        <v>1</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="I37" t="s">
+        <v>377</v>
+      </c>
+      <c r="M37" t="s">
+        <v>374</v>
+      </c>
+      <c r="N37" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14">
+      <c r="A38" t="s">
+        <v>379</v>
+      </c>
+      <c r="B38" s="8">
         <v>22</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="B10" s="8">
-        <v>1658</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="B11" s="8">
-        <v>2154</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="8">
-        <v>738</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="8">
-        <v>143</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="8">
-        <v>1971</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="8">
-        <v>208</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="B16" s="8">
-        <v>318</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="8">
-        <v>281</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="8">
-        <v>5</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="8">
-        <v>4071</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>272</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="8">
-        <v>39</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>53</v>
-      </c>
-      <c r="B22" s="8">
-        <v>16</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="B23" s="8">
-        <v>375</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="8">
-        <v>1</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="8">
-        <v>4</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="8">
-        <v>872</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="8">
-        <v>1156</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>81</v>
-      </c>
-      <c r="B28" s="8">
-        <v>16</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>83</v>
-      </c>
-      <c r="B29" s="8">
-        <v>839</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="8">
-        <v>130</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="8">
-        <v>68</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>95</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33" s="8">
-        <v>518</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>106</v>
-      </c>
-      <c r="B34" s="8">
-        <v>96</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="8">
-        <v>68</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>112</v>
-      </c>
-      <c r="B36" s="8">
-        <v>8</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>114</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>292</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>116</v>
-      </c>
-      <c r="B38" s="8">
-        <v>1</v>
-      </c>
       <c r="C38" s="9" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>380</v>
+      </c>
+      <c r="I38" t="s">
+        <v>381</v>
+      </c>
+      <c r="M38" t="s">
+        <v>369</v>
+      </c>
+      <c r="N38" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B39" s="8">
         <v>22</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>383</v>
+      </c>
+      <c r="I39" t="s">
+        <v>384</v>
+      </c>
+      <c r="M39" t="s">
+        <v>369</v>
+      </c>
+      <c r="N39" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B40" s="8">
-        <v>22</v>
+        <v>350</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>386</v>
+      </c>
+      <c r="I40" t="s">
+        <v>387</v>
+      </c>
+      <c r="M40" t="s">
+        <v>256</v>
+      </c>
+      <c r="N40" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B41" s="8">
-        <v>350</v>
+        <v>34</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>389</v>
+      </c>
+      <c r="I41" t="s">
+        <v>390</v>
+      </c>
+      <c r="M41" t="s">
+        <v>256</v>
+      </c>
+      <c r="N41" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>127</v>
-      </c>
-      <c r="B42" s="8">
-        <v>34</v>
+        <v>132</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>392</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>393</v>
+      </c>
+      <c r="I42" t="s">
+        <v>394</v>
+      </c>
+      <c r="M42" t="s">
+        <v>283</v>
+      </c>
+      <c r="N42" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>132</v>
-      </c>
-      <c r="B43" s="8" t="s">
-        <v>253</v>
+        <v>138</v>
+      </c>
+      <c r="B43" s="8">
+        <v>3643</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>396</v>
+      </c>
+      <c r="I43" t="s">
+        <v>397</v>
+      </c>
+      <c r="M43" t="s">
+        <v>398</v>
+      </c>
+      <c r="N43" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="B44" s="8">
-        <v>3643</v>
+        <v>30</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>159</v>
-      </c>
-      <c r="B45" s="8">
-        <v>30</v>
+        <v>400</v>
+      </c>
+      <c r="I44" t="s">
+        <v>401</v>
+      </c>
+      <c r="M44" t="s">
+        <v>256</v>
+      </c>
+      <c r="N44" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14">
+      <c r="A45" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>403</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>302</v>
+        <v>404</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="M45" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14">
+      <c r="A46" t="s">
+        <v>163</v>
+      </c>
+      <c r="B46" s="8">
+        <v>684</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
+        <v>407</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" t="s">
+        <v>408</v>
+      </c>
+      <c r="M46" t="s">
+        <v>398</v>
+      </c>
+      <c r="N46" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>163</v>
-      </c>
-      <c r="B47" s="8">
-        <v>684</v>
+        <v>161</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>410</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>304</v>
-      </c>
-      <c r="D47" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="I47" t="s">
+        <v>412</v>
+      </c>
+      <c r="M47" t="s">
+        <v>262</v>
+      </c>
+      <c r="N47" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="A48" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="M48" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N48" s="9" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="A49" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="B49" s="8">
+        <v>113</v>
+      </c>
+      <c r="C49" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="M49" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="N49" s="9" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>168</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="C50" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="I50" t="s">
+        <v>425</v>
+      </c>
+      <c r="M50" t="s">
+        <v>426</v>
+      </c>
+      <c r="N50" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51" t="s">
+        <v>169</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="C51" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="I51" t="s">
+        <v>430</v>
+      </c>
+      <c r="M51" t="s">
+        <v>431</v>
+      </c>
+      <c r="N51" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52" t="s">
+        <v>171</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="C52" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="I52" t="s">
+        <v>435</v>
+      </c>
+      <c r="M52" t="s">
+        <v>283</v>
+      </c>
+      <c r="N52" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53" t="s">
+        <v>172</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>438</v>
+      </c>
+      <c r="I53" t="s">
+        <v>439</v>
+      </c>
+      <c r="M53" t="s">
+        <v>283</v>
+      </c>
+      <c r="N53" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54" s="11" t="s">
+        <v>441</v>
+      </c>
+      <c r="B54" s="8">
+        <v>8</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>442</v>
+      </c>
+      <c r="D54" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>161</v>
-      </c>
-      <c r="B48" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="C49" s="9" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="9" t="s">
+      <c r="I54" s="11" t="s">
+        <v>443</v>
+      </c>
+      <c r="M54" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="B50" s="8">
-        <v>113</v>
-      </c>
-      <c r="C50" s="9" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" t="s">
-        <v>168</v>
-      </c>
-      <c r="B51" s="8" t="s">
-        <v>312</v>
-      </c>
-      <c r="C51" s="9" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>169</v>
-      </c>
-      <c r="B52" s="8" t="s">
-        <v>314</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
-      <c r="A53" t="s">
-        <v>171</v>
-      </c>
-      <c r="B53" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="A54" t="s">
-        <v>172</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="B55" s="8">
-        <v>8</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>321</v>
+      <c r="N54" s="11" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>447</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="56" spans="1:4">
+      <c r="I55" s="9" t="s">
+        <v>448</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56" s="9" t="s">
-        <v>322</v>
+        <v>450</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>324</v>
-      </c>
-      <c r="D56" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="I56" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="M56" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="N56" s="9" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57" t="s">
+        <v>188</v>
+      </c>
+      <c r="B57" s="8">
+        <v>27</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="I57" t="s">
+        <v>455</v>
+      </c>
+      <c r="M57" t="s">
+        <v>310</v>
+      </c>
+      <c r="N57" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>457</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="I58" t="s">
+        <v>459</v>
+      </c>
+      <c r="M58" t="s">
+        <v>310</v>
+      </c>
+      <c r="N58" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59" t="s">
+        <v>190</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="I59" t="s">
+        <v>463</v>
+      </c>
+      <c r="M59" t="s">
+        <v>262</v>
+      </c>
+      <c r="N59" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60" t="s">
+        <v>191</v>
+      </c>
+      <c r="B60" s="8">
+        <v>124</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="I60" t="s">
+        <v>421</v>
+      </c>
+      <c r="M60" t="s">
+        <v>256</v>
+      </c>
+      <c r="N60" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61" t="s">
+        <v>192</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>467</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="I61" t="s">
+        <v>469</v>
+      </c>
+      <c r="M61" t="s">
+        <v>310</v>
+      </c>
+      <c r="N61" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62" t="s">
+        <v>193</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="I62" t="s">
+        <v>473</v>
+      </c>
+      <c r="M62" t="s">
+        <v>474</v>
+      </c>
+      <c r="N62" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="B63" s="8">
+        <v>155</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>476</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="M63" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B64" s="8">
+        <v>20</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="I64" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="M64" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="N64" s="9" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14">
+      <c r="A65" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B65" s="8">
+        <v>5</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="D65" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="A57" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="A58" t="s">
-        <v>188</v>
-      </c>
-      <c r="B58" s="8">
-        <v>27</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="A59" t="s">
-        <v>189</v>
-      </c>
-      <c r="B59" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="C59" s="9" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="A60" t="s">
-        <v>190</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="A61" t="s">
-        <v>191</v>
-      </c>
-      <c r="B61" s="8">
-        <v>124</v>
-      </c>
-      <c r="C61" s="9" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="A62" t="s">
-        <v>192</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
-      <c r="A63" t="s">
-        <v>193</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C63" s="9" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
-      <c r="A64" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="B64" s="8">
-        <v>155</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
-      <c r="A65" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="B65" s="8">
-        <v>20</v>
-      </c>
-      <c r="C65" s="9" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="11" t="s">
-        <v>204</v>
+      <c r="I65" s="11" t="s">
+        <v>484</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>478</v>
+      </c>
+      <c r="N65" s="11" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" s="9" t="s">
+        <v>215</v>
       </c>
       <c r="B66" s="8">
-        <v>5</v>
+        <v>559</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>339</v>
-      </c>
-      <c r="D66" s="9" t="s">
+        <v>486</v>
+      </c>
+      <c r="I66" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="M66" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="N66" s="9" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14">
+      <c r="A67" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B67" s="8">
+        <v>1329</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="I67" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="68" spans="1:14">
+      <c r="A68" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B68" s="8">
+        <v>4</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="I68" s="9" t="s">
+        <v>492</v>
+      </c>
+      <c r="M68" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="N68" s="9" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14">
+      <c r="A69" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="B69" s="8">
+        <v>454</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="D69" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="67" spans="1:3">
-      <c r="A67" s="9" t="s">
-        <v>215</v>
-      </c>
-      <c r="B67" s="8">
-        <v>559</v>
-      </c>
-      <c r="C67" s="9" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
-      <c r="A68" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="B68" s="8">
-        <v>1329</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="B69" s="8">
-        <v>4</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+      <c r="I69" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="M69" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="N69" s="9" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14">
       <c r="A70" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B70" s="8">
-        <v>454</v>
+        <v>210</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>343</v>
+        <v>498</v>
       </c>
       <c r="D70" s="9" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="9" t="s">
-        <v>220</v>
+      <c r="I70" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="M70" s="9" t="s">
+        <v>478</v>
+      </c>
+      <c r="N70" s="9" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14">
+      <c r="A71" s="11" t="s">
+        <v>501</v>
       </c>
       <c r="B71" s="8">
-        <v>210</v>
+        <v>802</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>344</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
-      <c r="A72" s="11" t="s">
-        <v>345</v>
+        <v>502</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>503</v>
+      </c>
+      <c r="M71" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="N71" s="11" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="72" spans="1:14">
+      <c r="A72" s="9" t="s">
+        <v>222</v>
       </c>
       <c r="B72" s="8">
-        <v>802</v>
+        <v>0</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>504</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="M72" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="N72" s="9" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="73" spans="1:14">
       <c r="A73" s="9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B73" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" s="9" t="s">
-        <v>225</v>
+        <v>507</v>
+      </c>
+      <c r="I73" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="M73" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="N73" s="9" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="74" spans="1:14">
+      <c r="A74" s="11" t="s">
+        <v>197</v>
       </c>
       <c r="B74" s="8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>511</v>
+      </c>
+      <c r="I74" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="M74" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="N74" s="11" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="75" spans="1:14">
       <c r="A75" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B75" s="8">
         <v>4</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="B76" s="8">
-        <v>4</v>
+        <v>513</v>
+      </c>
+      <c r="I75" s="11" t="s">
+        <v>333</v>
+      </c>
+      <c r="M75" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="N75" s="11" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="76" ht="19" customHeight="1" spans="1:14">
+      <c r="A76" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>516</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="77" ht="19" customHeight="1" spans="1:3">
+        <v>517</v>
+      </c>
+      <c r="I76" s="9" t="s">
+        <v>518</v>
+      </c>
+      <c r="M76" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N76" s="9" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="77" ht="19" customHeight="1" spans="1:14">
       <c r="A77" s="9" t="s">
-        <v>351</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>352</v>
+        <v>520</v>
+      </c>
+      <c r="B77" s="8">
+        <v>325</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="78" ht="19" customHeight="1" spans="1:3">
+        <v>521</v>
+      </c>
+      <c r="I77" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="78" ht="19" customHeight="1" spans="1:14">
       <c r="A78" s="9" t="s">
-        <v>354</v>
+        <v>524</v>
       </c>
       <c r="B78" s="8">
-        <v>325</v>
+        <v>3052</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="79" ht="19" customHeight="1" spans="1:3">
+        <v>525</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="M78" s="9" t="s">
+        <v>527</v>
+      </c>
+      <c r="N78" s="9" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="79" ht="19" customHeight="1" spans="1:14">
       <c r="A79" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="B79" s="8">
-        <v>3052</v>
+        <v>529</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>530</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="80" ht="19" customHeight="1" spans="1:3">
+        <v>531</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="M79" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="N79" s="9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="80" ht="19" customHeight="1" spans="1:14">
       <c r="A80" s="9" t="s">
-        <v>358</v>
+        <v>533</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>359</v>
+        <v>534</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="81" ht="19" customHeight="1" spans="1:3">
+        <v>535</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="M80" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="N80" s="9" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="81" ht="19" customHeight="1" spans="1:14">
       <c r="A81" s="9" t="s">
-        <v>361</v>
+        <v>538</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>362</v>
+        <v>539</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="82" ht="19" customHeight="1" spans="1:3">
+        <v>540</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="M81" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="N81" s="9" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="82" ht="19" customHeight="1" spans="1:14">
       <c r="A82" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>365</v>
+        <v>544</v>
+      </c>
+      <c r="B82" s="8">
+        <v>-418</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="83" ht="19" customHeight="1" spans="1:3">
+        <v>545</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="M82" s="9" t="s">
+        <v>547</v>
+      </c>
+      <c r="N82" s="9" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="83" ht="19" customHeight="1" spans="1:14">
       <c r="A83" s="9" t="s">
-        <v>367</v>
+        <v>549</v>
       </c>
       <c r="B83" s="8">
-        <v>-418</v>
+        <v>576</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="84" ht="19" customHeight="1" spans="1:3">
+        <v>550</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>551</v>
+      </c>
+      <c r="M83" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="N83" s="9" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="84" ht="19" customHeight="1" spans="1:14">
       <c r="A84" s="9" t="s">
-        <v>369</v>
+        <v>554</v>
       </c>
       <c r="B84" s="8">
-        <v>576</v>
+        <v>4894</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="85" ht="19" customHeight="1" spans="1:3">
-      <c r="A85" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="B85" s="8">
-        <v>4894</v>
-      </c>
-      <c r="C85" s="9" t="s">
-        <v>372</v>
-      </c>
+        <v>555</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="M84" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="N84" s="9" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="85" ht="19" customHeight="1" spans="2:2">
+      <c r="B85" s="8"/>
     </row>
     <row r="86" ht="19" customHeight="1" spans="2:2">
       <c r="B86" s="8"/>
@@ -5311,7 +6768,7 @@
     <row r="89" ht="19" customHeight="1" spans="2:2">
       <c r="B89" s="8"/>
     </row>
-    <row r="90" ht="19" customHeight="1" spans="2:2">
+    <row r="90" spans="2:2">
       <c r="B90" s="8"/>
     </row>
     <row r="91" spans="2:2">
@@ -5652,9 +7109,6 @@
     </row>
     <row r="203" spans="2:2">
       <c r="B203" s="8"/>
-    </row>
-    <row r="204" spans="2:2">
-      <c r="B204" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5698,114 +7152,114 @@
   <sheetData>
     <row r="1" ht="15.75" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>373</v>
+        <v>559</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>374</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2" ht="15.75" spans="1:2">
       <c r="A2" s="3" t="s">
-        <v>375</v>
+        <v>561</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>376</v>
+        <v>562</v>
       </c>
     </row>
     <row r="3" ht="15.75" spans="1:2">
       <c r="A3" s="3" t="s">
-        <v>377</v>
+        <v>563</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>378</v>
+        <v>564</v>
       </c>
     </row>
     <row r="4" ht="15.75" spans="1:2">
       <c r="A4" s="3" t="s">
-        <v>379</v>
+        <v>565</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>380</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" ht="15.75" spans="1:2">
       <c r="A5" s="3" t="s">
-        <v>381</v>
+        <v>567</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>380</v>
+        <v>566</v>
       </c>
     </row>
     <row r="6" ht="15.75" spans="1:2">
       <c r="A6" s="4" t="s">
-        <v>382</v>
+        <v>568</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>383</v>
+        <v>569</v>
       </c>
     </row>
     <row r="7" ht="15.75" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>384</v>
+        <v>570</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>383</v>
+        <v>569</v>
       </c>
     </row>
     <row r="8" ht="15.75" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>385</v>
+        <v>571</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>383</v>
+        <v>569</v>
       </c>
     </row>
     <row r="9" ht="15.75" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>386</v>
+        <v>572</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>383</v>
+        <v>569</v>
       </c>
     </row>
     <row r="10" ht="15.75" spans="1:2">
       <c r="A10" s="3" t="s">
-        <v>387</v>
+        <v>573</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>383</v>
+        <v>569</v>
       </c>
     </row>
     <row r="11" ht="15.75" spans="1:2">
       <c r="A11" s="3" t="s">
-        <v>388</v>
+        <v>574</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>389</v>
+        <v>575</v>
       </c>
     </row>
     <row r="12" ht="15.75" spans="1:2">
       <c r="A12" s="3" t="s">
-        <v>390</v>
+        <v>576</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>391</v>
+        <v>577</v>
       </c>
     </row>
     <row r="13" ht="13.5" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>392</v>
+        <v>578</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>393</v>
+        <v>579</v>
       </c>
     </row>
     <row r="14" ht="13.5" spans="1:2">
       <c r="A14" s="5" t="s">
-        <v>394</v>
+        <v>580</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>393</v>
+        <v>579</v>
       </c>
     </row>
   </sheetData>
@@ -5827,92 +7281,92 @@
   <sheetData>
     <row r="1" ht="13.5" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>581</v>
       </c>
     </row>
     <row r="2" ht="13.5" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>396</v>
+        <v>582</v>
       </c>
     </row>
     <row r="3" ht="13.5" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>397</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" ht="13.5" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>398</v>
+        <v>584</v>
       </c>
     </row>
     <row r="5" ht="13.5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>399</v>
+        <v>585</v>
       </c>
     </row>
     <row r="6" ht="13.5" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>400</v>
+        <v>586</v>
       </c>
     </row>
     <row r="7" ht="13.5" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>401</v>
+        <v>587</v>
       </c>
     </row>
     <row r="8" ht="13.5" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>402</v>
+        <v>588</v>
       </c>
     </row>
     <row r="9" ht="13.5" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>403</v>
+        <v>589</v>
       </c>
     </row>
     <row r="10" ht="13.5" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>404</v>
+        <v>590</v>
       </c>
     </row>
     <row r="11" ht="13.5" spans="1:1">
       <c r="A11" s="1" t="s">
-        <v>405</v>
+        <v>591</v>
       </c>
     </row>
     <row r="12" ht="13.5" spans="1:1">
       <c r="A12" s="1" t="s">
-        <v>406</v>
+        <v>592</v>
       </c>
     </row>
     <row r="13" ht="13.5" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>407</v>
+        <v>593</v>
       </c>
     </row>
     <row r="14" ht="13.5" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>408</v>
+        <v>594</v>
       </c>
     </row>
     <row r="15" ht="13.5" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>409</v>
+        <v>595</v>
       </c>
     </row>
     <row r="16" ht="13.5" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>410</v>
+        <v>596</v>
       </c>
     </row>
     <row r="17" ht="13.5" spans="1:1">
       <c r="A17" s="2" t="s">
-        <v>411</v>
+        <v>597</v>
       </c>
     </row>
     <row r="18" ht="13.5" spans="1:1">
       <c r="A18" s="2" t="s">
-        <v>412</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -5934,27 +7388,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>413</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>414</v>
+        <v>600</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>415</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>416</v>
+        <v>602</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>417</v>
+        <v>603</v>
       </c>
     </row>
   </sheetData>
